--- a/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-02/report.xlsx
+++ b/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-02/report.xlsx
@@ -9,12 +9,10 @@
   <sheets>
     <sheet name="Usage Reporting" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Managed nodes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Indirectly Managed nodes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Infrastructure Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Usage by organizations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Usage by collections" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Usage by roles" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Usage by modules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Usage by organizations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Usage by collections" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Usage by roles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Usage by modules" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +538,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Updated: Aug 26, 2026</t>
+          <t>Updated: Sep 18, 2026</t>
         </is>
       </c>
     </row>
@@ -935,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -949,60 +947,69 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Host name</t>
+          <t>Organization name</t>
         </is>
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>Automated by
-organizations</t>
+          <t>Job runs</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>Job runs</t>
+          <t>Unique managed nodes
+automated</t>
         </is>
       </c>
       <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Non-unique managed
+nodes automated</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Number of task
 runs</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>First
-automation</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>Last
-automation</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>Canonical
-Facts</t>
-        </is>
-      </c>
-      <c r="H1" s="14" t="inlineStr">
-        <is>
-          <t>Facts</t>
-        </is>
-      </c>
-      <c r="I1" s="14" t="inlineStr">
-        <is>
-          <t>Manage
-Node
-Types</t>
-        </is>
-      </c>
-      <c r="J1" s="14" t="inlineStr">
-        <is>
-          <t>Events</t>
-        </is>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>test organization</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1016,35 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>No indirect nodes found</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1058,93 +1037,85 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Organization name</t>
+          <t>Collection name</t>
         </is>
       </c>
       <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Job runs</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Unique managed nodes
 automated</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Non-unique managed
 nodes automated</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Unique indirect managed nodes
-automated</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique indirect managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Number of task
 runs</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="15" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>test organization</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15" t="n">
-        <v>8</v>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Duration of task
+runs [seconds]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Role name</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Unique managed nodes
+automated</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Non-unique managed
+nodes automated</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Number of task
+runs</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Duration of task
+runs [seconds]</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1172,112 +1143,6 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Collection name</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Unique managed nodes
-automated</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Number of task
-runs</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Duration of task
-runs [seconds]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Role name</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Unique managed nodes
-automated</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Number of task
-runs</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Duration of task
-runs [seconds]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
           <t>Module name</t>
         </is>
       </c>

--- a/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-02/report.xlsx
+++ b/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-02/report.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet name="Usage Reporting" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Managed nodes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Usage by organizations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Usage by collections" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Usage by roles" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Usage by modules" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Indirectly Managed nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Infrastructure Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Usage by organizations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Usage by collections" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Usage by roles" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Usage by modules" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,7 +540,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Updated: Sep 18, 2026</t>
+          <t>Updated: Aug 26, 2026</t>
         </is>
       </c>
     </row>
@@ -933,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -947,69 +949,60 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Organization name</t>
+          <t>Host name</t>
         </is>
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
+          <t>Automated by
+organizations</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
           <t>Job runs</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Unique managed nodes
-automated</t>
-        </is>
-      </c>
       <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Number of task
 runs</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="15" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>test organization</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>8</v>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>First
+automation</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Last
+automation</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>Canonical
+Facts</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>Manage
+Node
+Types</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +1016,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>No indirect nodes found</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1037,85 +1058,93 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Collection name</t>
+          <t>Organization name</t>
         </is>
       </c>
       <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Job runs</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Unique managed nodes
 automated</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Non-unique managed
 nodes automated</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Unique indirect managed nodes
+automated</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Non-unique indirect managed
+nodes automated</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Number of task
 runs</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Duration of task
-runs [seconds]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Role name</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Unique managed nodes
-automated</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Number of task
-runs</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Duration of task
-runs [seconds]</t>
-        </is>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>test organization</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1143,6 +1172,112 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
+          <t>Collection name</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Unique managed nodes
+automated</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Non-unique managed
+nodes automated</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Number of task
+runs</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Duration of task
+runs [seconds]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Role name</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Unique managed nodes
+automated</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Non-unique managed
+nodes automated</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Number of task
+runs</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Duration of task
+runs [seconds]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
           <t>Module name</t>
         </is>
       </c>

--- a/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-02/report.xlsx
+++ b/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-02/report.xlsx
@@ -9,12 +9,7 @@
   <sheets>
     <sheet name="Usage Reporting" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Managed nodes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Indirectly Managed nodes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Infrastructure Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Usage by organizations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Usage by collections" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Usage by roles" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Usage by modules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Usage by organizations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +535,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Updated: Aug 26, 2026</t>
+          <t>Updated: Mar 04, 2025</t>
         </is>
       </c>
     </row>
@@ -935,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -949,153 +944,32 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Host name</t>
+          <t>Organization name</t>
         </is>
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>Automated by
-organizations</t>
+          <t>Job runs</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>Job runs</t>
+          <t>Unique managed nodes
+automated</t>
         </is>
       </c>
       <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Non-unique managed
+nodes automated</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Number of task
 runs</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>First
-automation</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>Last
-automation</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>Canonical
-Facts</t>
-        </is>
-      </c>
-      <c r="H1" s="14" t="inlineStr">
-        <is>
-          <t>Facts</t>
-        </is>
-      </c>
-      <c r="I1" s="14" t="inlineStr">
-        <is>
-          <t>Manage
-Node
-Types</t>
-        </is>
-      </c>
-      <c r="J1" s="14" t="inlineStr">
-        <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>No indirect nodes found</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Organization name</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Job runs</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Unique managed nodes
-automated</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Unique indirect managed nodes
-automated</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique indirect managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>Number of task
-runs</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
@@ -1113,12 +987,6 @@
         <v>2</v>
       </c>
       <c r="E2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="15" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1138,172 +1006,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15" t="n">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Collection name</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Unique managed nodes
-automated</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Number of task
-runs</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Duration of task
-runs [seconds]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Role name</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Unique managed nodes
-automated</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Number of task
-runs</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Duration of task
-runs [seconds]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Module name</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Unique managed nodes
-automated</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Non-unique managed
-nodes automated</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Number of task
-runs</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Duration of task
-runs [seconds]</t>
-        </is>
       </c>
     </row>
   </sheetData>
